--- a/data/output/ALL3_TestRMSE00241/pureComponents_filled_testing_predicted_v3.xlsx
+++ b/data/output/ALL3_TestRMSE00241/pureComponents_filled_testing_predicted_v3.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\aglotov\Eutectics\data\output\ALL3_TestRMSE00241\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5590F8-1A51-4DA8-8FF9-0AC7DBAEACBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D1E9A9-A99D-40CA-A7B9-288535106E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25680" yWindow="1485" windowWidth="21600" windowHeight="14715" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pure Input" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Full Name</t>
   </si>
@@ -61,9 +74,6 @@
     <t>ammonia borane</t>
   </si>
   <si>
-    <t>[BH3-][NH3+]</t>
-  </si>
-  <si>
     <t>tetramethylammonium borohydride</t>
   </si>
   <si>
@@ -76,18 +86,6 @@
     <t>[BH4-].CCCC[N+](CCCC)(CCCC)CCCC</t>
   </si>
   <si>
-    <t>tetraethylammonium bromide</t>
-  </si>
-  <si>
-    <t>CC[N+](CC)(CC)CC.[Br-]</t>
-  </si>
-  <si>
-    <t>tetramethylammonium chloride</t>
-  </si>
-  <si>
-    <t>C[N+](C)(C)C.[Cl-]</t>
-  </si>
-  <si>
     <t>tetraethylammonium borohydride</t>
   </si>
   <si>
@@ -98,6 +96,9 @@
   </si>
   <si>
     <t>[BH4-].CCC[N+](CCC)(CCC)CCC</t>
+  </si>
+  <si>
+    <t>B.N</t>
   </si>
 </sst>
 </file>
@@ -133,8 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -438,8 +438,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="32.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -480,166 +483,133 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1">
-        <v>176.1963782899328</v>
-      </c>
-      <c r="E2" s="1">
-        <v>32.307655124188088</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1">
-        <v>3.9706178513163439</v>
-      </c>
-      <c r="H2" s="1">
-        <v>4.6840953006963861</v>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2">
+        <v>385.11282360982568</v>
+      </c>
+      <c r="E2">
+        <v>65.726936839172097</v>
+      </c>
+      <c r="G2">
+        <v>6.882859913913121</v>
+      </c>
+      <c r="H2">
+        <v>7.6506770311446699</v>
       </c>
       <c r="J2">
-        <v>-268.16997940178931</v>
+        <v>-138.02669614825061</v>
+      </c>
+      <c r="K2">
+        <v>18.351140896132279</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1">
-        <v>519.01506655898004</v>
-      </c>
-      <c r="E3" s="1">
-        <v>61.407092477557889</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1">
-        <v>10.50253330246275</v>
-      </c>
-      <c r="H3" s="1">
-        <v>7.1513896754279038</v>
+      <c r="D3">
+        <v>563.71773849019746</v>
+      </c>
+      <c r="E3">
+        <v>50.77717755567101</v>
+      </c>
+      <c r="G3">
+        <v>19.25645796902565</v>
+      </c>
+      <c r="H3">
+        <v>7.3990823500233693</v>
       </c>
       <c r="J3">
-        <v>-172.92763055807839</v>
+        <v>-304.17380342343478</v>
+      </c>
+      <c r="K3">
+        <v>13.260150394489081</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="1">
-        <v>436.36877714107698</v>
-      </c>
-      <c r="E4" s="1">
-        <v>34.447600453670198</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1">
-        <v>17.676996338258821</v>
-      </c>
-      <c r="H4" s="1">
-        <v>5.9173053127932844</v>
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>548.02778012861222</v>
+      </c>
+      <c r="E4">
+        <v>37.614824236944223</v>
+      </c>
+      <c r="G4">
+        <v>18.482740785606531</v>
+      </c>
+      <c r="H4">
+        <v>5.4913737522370552</v>
       </c>
       <c r="J4">
-        <v>-352.85165216874248</v>
+        <v>-405.53613979528262</v>
+      </c>
+      <c r="K4">
+        <v>13.24004078970907</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1">
-        <v>440.71426614446858</v>
-      </c>
-      <c r="E5" s="1">
-        <v>26.734032890637032</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1">
-        <v>43.286140593640503</v>
-      </c>
-      <c r="H5" s="1">
-        <v>7.1513446018453486</v>
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>516.02091904459292</v>
+      </c>
+      <c r="E5">
+        <v>44.172697973658082</v>
+      </c>
+      <c r="G5">
+        <v>11.33799404304005</v>
+      </c>
+      <c r="H5">
+        <v>5.2973651472068877</v>
+      </c>
+      <c r="J5">
+        <v>-471.24293725318569</v>
+      </c>
+      <c r="K5">
+        <v>13.24917033613808</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="1">
-        <v>571.73086348535026</v>
-      </c>
-      <c r="E6" s="1">
-        <v>27.320226553705801</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1">
-        <v>19.402393344372651</v>
-      </c>
-      <c r="H6" s="1">
-        <v>3.9010948195706532</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="1">
-        <v>440.23629612133959</v>
-      </c>
-      <c r="E7" s="1">
-        <v>26.407526340745392</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1">
-        <v>44.292587682727657</v>
-      </c>
-      <c r="H7" s="1">
-        <v>7.151352328765392</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="1">
-        <v>464.58871159968771</v>
-      </c>
-      <c r="E8" s="1">
-        <v>41.010279406745163</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1">
-        <v>13.94791019877724</v>
-      </c>
-      <c r="H8" s="1">
-        <v>5.9741188701557579</v>
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>380.97078383198038</v>
+      </c>
+      <c r="E6">
+        <v>24.718564070807439</v>
+      </c>
+      <c r="G6">
+        <v>18.725346771421421</v>
+      </c>
+      <c r="H6">
+        <v>4.7794628154957133</v>
+      </c>
+      <c r="J6">
+        <v>-471.25237495076959</v>
+      </c>
+      <c r="K6">
+        <v>13.36538660900019</v>
       </c>
     </row>
   </sheetData>
